--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1482,6 +1482,27 @@
       </c>
       <c r="E48" s="7">
         <f>C48-C47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1516</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5130</v>
+      </c>
+      <c r="D49" s="7">
+        <f>B49-B48</f>
+        <v/>
+      </c>
+      <c r="E49" s="7">
+        <f>C49-C48</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1503,6 +1503,27 @@
       </c>
       <c r="E49" s="7">
         <f>C49-C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1522</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5140</v>
+      </c>
+      <c r="D50" s="7">
+        <f>B50-B49</f>
+        <v/>
+      </c>
+      <c r="E50" s="7">
+        <f>C50-C49</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1524,6 +1524,27 @@
       </c>
       <c r="E50" s="7">
         <f>C50-C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5150</v>
+      </c>
+      <c r="D51" s="7">
+        <f>B51-B50</f>
+        <v/>
+      </c>
+      <c r="E51" s="7">
+        <f>C51-C50</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1545,6 +1545,27 @@
       </c>
       <c r="E51" s="7">
         <f>C51-C50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5150</v>
+      </c>
+      <c r="D52" s="7">
+        <f>B52-B51</f>
+        <v/>
+      </c>
+      <c r="E52" s="7">
+        <f>C52-C51</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1566,6 +1566,27 @@
       </c>
       <c r="E52" s="7">
         <f>C52-C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5150</v>
+      </c>
+      <c r="D53" s="7">
+        <f>B53-B52</f>
+        <v/>
+      </c>
+      <c r="E53" s="7">
+        <f>C53-C52</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1587,6 +1587,27 @@
       </c>
       <c r="E53" s="7">
         <f>C53-C52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1521</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5160</v>
+      </c>
+      <c r="D54" s="7">
+        <f>B54-B53</f>
+        <v/>
+      </c>
+      <c r="E54" s="7">
+        <f>C54-C53</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1608,6 +1608,27 @@
       </c>
       <c r="E54" s="7">
         <f>C54-C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1520</v>
+      </c>
+      <c r="C55" t="n">
+        <v>5170</v>
+      </c>
+      <c r="D55" s="7">
+        <f>B55-B54</f>
+        <v/>
+      </c>
+      <c r="E55" s="7">
+        <f>C55-C54</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1629,6 +1629,27 @@
       </c>
       <c r="E55" s="7">
         <f>C55-C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1520</v>
+      </c>
+      <c r="C56" t="n">
+        <v>5180</v>
+      </c>
+      <c r="D56" s="7">
+        <f>B56-B55</f>
+        <v/>
+      </c>
+      <c r="E56" s="7">
+        <f>C56-C55</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1650,6 +1650,27 @@
       </c>
       <c r="E56" s="7">
         <f>C56-C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1521</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5190</v>
+      </c>
+      <c r="D57" s="7">
+        <f>B57-B56</f>
+        <v/>
+      </c>
+      <c r="E57" s="7">
+        <f>C57-C56</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1671,6 +1671,27 @@
       </c>
       <c r="E57" s="7">
         <f>C57-C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5190</v>
+      </c>
+      <c r="D58" s="7">
+        <f>B58-B57</f>
+        <v/>
+      </c>
+      <c r="E58" s="7">
+        <f>C58-C57</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1692,6 +1692,27 @@
       </c>
       <c r="E58" s="7">
         <f>C58-C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1527</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D59" s="7">
+        <f>B59-B58</f>
+        <v/>
+      </c>
+      <c r="E59" s="7">
+        <f>C59-C58</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1713,6 +1713,27 @@
       </c>
       <c r="E59" s="7">
         <f>C59-C58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1530</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5230</v>
+      </c>
+      <c r="D60" s="7">
+        <f>B60-B59</f>
+        <v/>
+      </c>
+      <c r="E60" s="7">
+        <f>C60-C59</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1734,6 +1734,27 @@
       </c>
       <c r="E60" s="7">
         <f>C60-C59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1534</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5240</v>
+      </c>
+      <c r="D61" s="7">
+        <f>B61-B60</f>
+        <v/>
+      </c>
+      <c r="E61" s="7">
+        <f>C61-C60</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1755,6 +1755,27 @@
       </c>
       <c r="E61" s="7">
         <f>C61-C60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1536</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5240</v>
+      </c>
+      <c r="D62" s="7">
+        <f>B62-B61</f>
+        <v/>
+      </c>
+      <c r="E62" s="7">
+        <f>C62-C61</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1776,6 +1776,27 @@
       </c>
       <c r="E62" s="7">
         <f>C62-C61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1536</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5240</v>
+      </c>
+      <c r="D63" s="7">
+        <f>B63-B62</f>
+        <v/>
+      </c>
+      <c r="E63" s="7">
+        <f>C63-C62</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1797,6 +1797,27 @@
       </c>
       <c r="E63" s="7">
         <f>C63-C62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1536</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5240</v>
+      </c>
+      <c r="D64" s="7">
+        <f>B64-B63</f>
+        <v/>
+      </c>
+      <c r="E64" s="7">
+        <f>C64-C63</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1818,6 +1818,27 @@
       </c>
       <c r="E64" s="7">
         <f>C64-C63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1536</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5240</v>
+      </c>
+      <c r="D65" s="7">
+        <f>B65-B64</f>
+        <v/>
+      </c>
+      <c r="E65" s="7">
+        <f>C65-C64</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1840,6 +1840,23 @@
       <c r="E65" s="7">
         <f>C65-C64</f>
         <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1857,6 +1857,19 @@
         <is>
           <t>取得失敗</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1533</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5250</v>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1870,6 +1870,27 @@
       </c>
       <c r="C67" t="n">
         <v>5250</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1531</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D68" s="7">
+        <f>B68-B67</f>
+        <v/>
+      </c>
+      <c r="E68" s="7">
+        <f>C68-C67</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1890,6 +1890,27 @@
       </c>
       <c r="E68" s="7">
         <f>C68-C67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1533</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D69" s="7">
+        <f>B69-B68</f>
+        <v/>
+      </c>
+      <c r="E69" s="7">
+        <f>C69-C68</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1911,6 +1911,27 @@
       </c>
       <c r="E69" s="7">
         <f>C69-C68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1535</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5260</v>
+      </c>
+      <c r="D70" s="7">
+        <f>B70-B69</f>
+        <v/>
+      </c>
+      <c r="E70" s="7">
+        <f>C70-C69</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1932,6 +1932,27 @@
       </c>
       <c r="E70" s="7">
         <f>C70-C69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1533</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5260</v>
+      </c>
+      <c r="D71" s="7">
+        <f>B71-B70</f>
+        <v/>
+      </c>
+      <c r="E71" s="7">
+        <f>C71-C70</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1953,6 +1953,25 @@
       </c>
       <c r="E71" s="7">
         <f>C71-C70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1534</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="D72" s="7">
+        <f>B72-B71</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1972,6 +1972,23 @@
       </c>
       <c r="D72" s="7">
         <f>B72-B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1536</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5270</v>
+      </c>
+      <c r="D73" s="7">
+        <f>B73-B72</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1989,6 +1989,25 @@
       </c>
       <c r="D73" s="7">
         <f>B73-B72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1533</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="D74" s="7">
+        <f>B74-B73</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2009,6 +2009,23 @@
       <c r="D74" s="7">
         <f>B74-B73</f>
         <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2026,6 +2026,19 @@
         <is>
           <t>取得失敗</t>
         </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1537</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5280</v>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2039,27 @@
       </c>
       <c r="C76" t="n">
         <v>5280</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1541</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5290</v>
+      </c>
+      <c r="D77" s="7">
+        <f>B77-B76</f>
+        <v/>
+      </c>
+      <c r="E77" s="7">
+        <f>C77-C76</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2059,6 +2059,27 @@
       </c>
       <c r="E77" s="7">
         <f>C77-C76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1541</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5300</v>
+      </c>
+      <c r="D78" s="7">
+        <f>B78-B77</f>
+        <v/>
+      </c>
+      <c r="E78" s="7">
+        <f>C78-C77</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2080,27 @@
       </c>
       <c r="E78" s="7">
         <f>C78-C77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D79" s="7">
+        <f>B79-B78</f>
+        <v/>
+      </c>
+      <c r="E79" s="7">
+        <f>C79-C78</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,27 @@
       </c>
       <c r="E79" s="7">
         <f>C79-C78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1541</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D80" s="7">
+        <f>B80-B79</f>
+        <v/>
+      </c>
+      <c r="E80" s="7">
+        <f>C80-C79</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2122,6 +2122,27 @@
       </c>
       <c r="E80" s="7">
         <f>C80-C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1547</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D81" s="7">
+        <f>B81-B80</f>
+        <v/>
+      </c>
+      <c r="E81" s="7">
+        <f>C81-C80</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2143,6 +2143,27 @@
       </c>
       <c r="E81" s="7">
         <f>C81-C80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1550</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D82" s="7">
+        <f>B82-B81</f>
+        <v/>
+      </c>
+      <c r="E82" s="7">
+        <f>C82-C81</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2165,23 @@
       <c r="E82" s="7">
         <f>C82-C81</f>
         <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2182,19 @@
         <is>
           <t>取得失敗</t>
         </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1555</v>
+      </c>
+      <c r="C84" t="n">
+        <v>5320</v>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2195,27 @@
       </c>
       <c r="C84" t="n">
         <v>5320</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1556</v>
+      </c>
+      <c r="C85" t="n">
+        <v>5320</v>
+      </c>
+      <c r="D85" s="7">
+        <f>B85-B84</f>
+        <v/>
+      </c>
+      <c r="E85" s="7">
+        <f>C85-C84</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2215,6 +2215,27 @@
       </c>
       <c r="E85" s="7">
         <f>C85-C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1556</v>
+      </c>
+      <c r="C86" t="n">
+        <v>5320</v>
+      </c>
+      <c r="D86" s="7">
+        <f>B86-B85</f>
+        <v/>
+      </c>
+      <c r="E86" s="7">
+        <f>C86-C85</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2236,6 +2236,27 @@
       </c>
       <c r="E86" s="7">
         <f>C86-C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1555</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5340</v>
+      </c>
+      <c r="D87" s="7">
+        <f>B87-B86</f>
+        <v/>
+      </c>
+      <c r="E87" s="7">
+        <f>C87-C86</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2257,27 @@
       </c>
       <c r="E87" s="7">
         <f>C87-C86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1572</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5350</v>
+      </c>
+      <c r="D88" s="7">
+        <f>B88-B87</f>
+        <v/>
+      </c>
+      <c r="E88" s="7">
+        <f>C88-C87</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2278,6 +2278,27 @@
       </c>
       <c r="E88" s="7">
         <f>C88-C87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5380</v>
+      </c>
+      <c r="D89" s="7">
+        <f>B89-B88</f>
+        <v/>
+      </c>
+      <c r="E89" s="7">
+        <f>C89-C88</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2299,6 +2299,27 @@
       </c>
       <c r="E89" s="7">
         <f>C89-C88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1589</v>
+      </c>
+      <c r="C90" t="n">
+        <v>5420</v>
+      </c>
+      <c r="D90" s="7">
+        <f>B90-B89</f>
+        <v/>
+      </c>
+      <c r="E90" s="7">
+        <f>C90-C89</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2320,6 +2320,27 @@
       </c>
       <c r="E90" s="7">
         <f>C90-C89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1602</v>
+      </c>
+      <c r="C91" t="n">
+        <v>5450</v>
+      </c>
+      <c r="D91" s="7">
+        <f>B91-B90</f>
+        <v/>
+      </c>
+      <c r="E91" s="7">
+        <f>C91-C90</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2341,6 +2341,27 @@
       </c>
       <c r="E91" s="7">
         <f>C91-C90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1610</v>
+      </c>
+      <c r="C92" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D92" s="7">
+        <f>B92-B91</f>
+        <v/>
+      </c>
+      <c r="E92" s="7">
+        <f>C92-C91</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2362,6 +2362,27 @@
       </c>
       <c r="E92" s="7">
         <f>C92-C91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1614</v>
+      </c>
+      <c r="C93" t="n">
+        <v>5530</v>
+      </c>
+      <c r="D93" s="7">
+        <f>B93-B92</f>
+        <v/>
+      </c>
+      <c r="E93" s="7">
+        <f>C93-C92</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2383,6 +2383,27 @@
       </c>
       <c r="E93" s="7">
         <f>C93-C92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1619</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5590</v>
+      </c>
+      <c r="D94" s="7">
+        <f>B94-B93</f>
+        <v/>
+      </c>
+      <c r="E94" s="7">
+        <f>C94-C93</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2404,6 +2404,27 @@
       </c>
       <c r="E94" s="7">
         <f>C94-C93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C95" t="n">
+        <v>5630</v>
+      </c>
+      <c r="D95" s="7">
+        <f>B95-B94</f>
+        <v/>
+      </c>
+      <c r="E95" s="7">
+        <f>C95-C94</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2425,6 +2425,27 @@
       </c>
       <c r="E95" s="7">
         <f>C95-C94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C96" t="n">
+        <v>5640</v>
+      </c>
+      <c r="D96" s="7">
+        <f>B96-B95</f>
+        <v/>
+      </c>
+      <c r="E96" s="7">
+        <f>C96-C95</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2446,6 +2446,27 @@
       </c>
       <c r="E96" s="7">
         <f>C96-C95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1629</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5680</v>
+      </c>
+      <c r="D97" s="7">
+        <f>B97-B96</f>
+        <v/>
+      </c>
+      <c r="E97" s="7">
+        <f>C97-C96</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2467,6 +2467,27 @@
       </c>
       <c r="E97" s="7">
         <f>C97-C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1629</v>
+      </c>
+      <c r="C98" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D98" s="7">
+        <f>B98-B97</f>
+        <v/>
+      </c>
+      <c r="E98" s="7">
+        <f>C98-C97</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2488,6 +2488,27 @@
       </c>
       <c r="E98" s="7">
         <f>C98-C97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1630</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5730</v>
+      </c>
+      <c r="D99" s="7">
+        <f>B99-B98</f>
+        <v/>
+      </c>
+      <c r="E99" s="7">
+        <f>C99-C98</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2509,6 +2509,27 @@
       </c>
       <c r="E99" s="7">
         <f>C99-C98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1635</v>
+      </c>
+      <c r="C100" t="n">
+        <v>5750</v>
+      </c>
+      <c r="D100" s="7">
+        <f>B100-B99</f>
+        <v/>
+      </c>
+      <c r="E100" s="7">
+        <f>C100-C99</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2530,6 +2530,27 @@
       </c>
       <c r="E100" s="7">
         <f>C100-C99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1636</v>
+      </c>
+      <c r="C101" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D101" s="7">
+        <f>B101-B100</f>
+        <v/>
+      </c>
+      <c r="E101" s="7">
+        <f>C101-C100</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2551,6 +2551,27 @@
       </c>
       <c r="E101" s="7">
         <f>C101-C100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1634</v>
+      </c>
+      <c r="C102" t="n">
+        <v>5810</v>
+      </c>
+      <c r="D102" s="7">
+        <f>B102-B101</f>
+        <v/>
+      </c>
+      <c r="E102" s="7">
+        <f>C102-C101</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2572,6 +2572,27 @@
       </c>
       <c r="E102" s="7">
         <f>C102-C101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1634</v>
+      </c>
+      <c r="C103" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D103" s="7">
+        <f>B103-B102</f>
+        <v/>
+      </c>
+      <c r="E103" s="7">
+        <f>C103-C102</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2593,6 +2593,25 @@
       </c>
       <c r="E103" s="7">
         <f>C103-C102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1634</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="D104" s="7">
+        <f>B104-B103</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2612,6 +2612,23 @@
       </c>
       <c r="D104" s="7">
         <f>B104-B103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1638</v>
+      </c>
+      <c r="C105" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D105" s="7">
+        <f>B105-B104</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2629,6 +2629,27 @@
       </c>
       <c r="D105" s="7">
         <f>B105-B104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1636</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5890</v>
+      </c>
+      <c r="D106" s="7">
+        <f>B106-B105</f>
+        <v/>
+      </c>
+      <c r="E106" s="7">
+        <f>C106-C105</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2650,6 +2650,27 @@
       </c>
       <c r="E106" s="7">
         <f>C106-C105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1639</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5890</v>
+      </c>
+      <c r="D107" s="7">
+        <f>B107-B106</f>
+        <v/>
+      </c>
+      <c r="E107" s="7">
+        <f>C107-C106</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2672,6 +2672,23 @@
       <c r="E107" s="7">
         <f>C107-C106</f>
         <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2689,6 +2689,19 @@
         <is>
           <t>取得失敗</t>
         </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1638</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5910</v>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2702,6 +2702,27 @@
       </c>
       <c r="C109" t="n">
         <v>5910</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1639</v>
+      </c>
+      <c r="C110" t="n">
+        <v>5910</v>
+      </c>
+      <c r="D110" s="7">
+        <f>B110-B109</f>
+        <v/>
+      </c>
+      <c r="E110" s="7">
+        <f>C110-C109</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2722,6 +2722,27 @@
       </c>
       <c r="E110" s="7">
         <f>C110-C109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1644</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5920</v>
+      </c>
+      <c r="D111" s="7">
+        <f>B111-B110</f>
+        <v/>
+      </c>
+      <c r="E111" s="7">
+        <f>C111-C110</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2743,6 +2743,27 @@
       </c>
       <c r="E111" s="7">
         <f>C111-C110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1647</v>
+      </c>
+      <c r="C112" t="n">
+        <v>5930</v>
+      </c>
+      <c r="D112" s="7">
+        <f>B112-B111</f>
+        <v/>
+      </c>
+      <c r="E112" s="7">
+        <f>C112-C111</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2764,6 +2764,27 @@
       </c>
       <c r="E112" s="7">
         <f>C112-C111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1648</v>
+      </c>
+      <c r="C113" t="n">
+        <v>5930</v>
+      </c>
+      <c r="D113" s="7">
+        <f>B113-B112</f>
+        <v/>
+      </c>
+      <c r="E113" s="7">
+        <f>C113-C112</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2785,6 +2785,27 @@
       </c>
       <c r="E113" s="7">
         <f>C113-C112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1649</v>
+      </c>
+      <c r="C114" t="n">
+        <v>5940</v>
+      </c>
+      <c r="D114" s="7">
+        <f>B114-B113</f>
+        <v/>
+      </c>
+      <c r="E114" s="7">
+        <f>C114-C113</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2806,6 +2806,27 @@
       </c>
       <c r="E114" s="7">
         <f>C114-C113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1649</v>
+      </c>
+      <c r="C115" t="n">
+        <v>5950</v>
+      </c>
+      <c r="D115" s="7">
+        <f>B115-B114</f>
+        <v/>
+      </c>
+      <c r="E115" s="7">
+        <f>C115-C114</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2827,6 +2827,27 @@
       </c>
       <c r="E115" s="7">
         <f>C115-C114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1649</v>
+      </c>
+      <c r="C116" t="n">
+        <v>5950</v>
+      </c>
+      <c r="D116" s="7">
+        <f>B116-B115</f>
+        <v/>
+      </c>
+      <c r="E116" s="7">
+        <f>C116-C115</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2848,6 +2848,27 @@
       </c>
       <c r="E116" s="7">
         <f>C116-C115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1648</v>
+      </c>
+      <c r="C117" t="n">
+        <v>5960</v>
+      </c>
+      <c r="D117" s="7">
+        <f>B117-B116</f>
+        <v/>
+      </c>
+      <c r="E117" s="7">
+        <f>C117-C116</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2869,6 +2869,27 @@
       </c>
       <c r="E117" s="7">
         <f>C117-C116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1649</v>
+      </c>
+      <c r="C118" t="n">
+        <v>5970</v>
+      </c>
+      <c r="D118" s="7">
+        <f>B118-B117</f>
+        <v/>
+      </c>
+      <c r="E118" s="7">
+        <f>C118-C117</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2890,6 +2890,27 @@
       </c>
       <c r="E118" s="7">
         <f>C118-C117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1651</v>
+      </c>
+      <c r="C119" t="n">
+        <v>5970</v>
+      </c>
+      <c r="D119" s="7">
+        <f>B119-B118</f>
+        <v/>
+      </c>
+      <c r="E119" s="7">
+        <f>C119-C118</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2911,6 +2911,27 @@
       </c>
       <c r="E119" s="7">
         <f>C119-C118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1654</v>
+      </c>
+      <c r="C120" t="n">
+        <v>5970</v>
+      </c>
+      <c r="D120" s="7">
+        <f>B120-B119</f>
+        <v/>
+      </c>
+      <c r="E120" s="7">
+        <f>C120-C119</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2932,6 +2932,27 @@
       </c>
       <c r="E120" s="7">
         <f>C120-C119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1656</v>
+      </c>
+      <c r="C121" t="n">
+        <v>5980</v>
+      </c>
+      <c r="D121" s="7">
+        <f>B121-B120</f>
+        <v/>
+      </c>
+      <c r="E121" s="7">
+        <f>C121-C120</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2953,6 +2953,27 @@
       </c>
       <c r="E121" s="7">
         <f>C121-C120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1659</v>
+      </c>
+      <c r="C122" t="n">
+        <v>5980</v>
+      </c>
+      <c r="D122" s="7">
+        <f>B122-B121</f>
+        <v/>
+      </c>
+      <c r="E122" s="7">
+        <f>C122-C121</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2974,6 +2974,27 @@
       </c>
       <c r="E122" s="7">
         <f>C122-C121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1659</v>
+      </c>
+      <c r="C123" t="n">
+        <v>5990</v>
+      </c>
+      <c r="D123" s="7">
+        <f>B123-B122</f>
+        <v/>
+      </c>
+      <c r="E123" s="7">
+        <f>C123-C122</f>
         <v/>
       </c>
     </row>
